--- a/skillmap/スキルマップ.xlsx
+++ b/skillmap/スキルマップ.xlsx
@@ -338,6 +338,102 @@
             </numRef>
           </val>
         </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'サマリー'!E3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'サマリー'!$A$4:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'サマリー'!$E$4:$E$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'サマリー'!F3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'サマリー'!$A$4:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'サマリー'!$F$4:$F$9</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'サマリー'!G3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'サマリー'!$A$4:$A$9</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'サマリー'!$G$4:$G$9</f>
+            </numRef>
+          </val>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </radarChart>
@@ -382,7 +478,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -694,7 +790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -702,9 +798,15 @@
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -754,15 +856,45 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Fとの差</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>HSとの差</t>
+          <t>M</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>F差</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HS差</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>H差</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>M差</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>K差</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>メモ</t>
         </is>
@@ -784,15 +916,30 @@
       </c>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="7" t="n"/>
-      <c r="F5" s="8">
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="8">
         <f>IF(D5="","",D5-C5)</f>
         <v/>
       </c>
-      <c r="G5" s="8">
+      <c r="J5" s="8">
         <f>IF(E5="","",E5-C5)</f>
         <v/>
       </c>
-      <c r="H5" s="6" t="n"/>
+      <c r="K5" s="8">
+        <f>IF(F5="","",F5-C5)</f>
+        <v/>
+      </c>
+      <c r="L5" s="8">
+        <f>IF(G5="","",G5-C5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="8">
+        <f>IF(H5="","",H5-C5)</f>
+        <v/>
+      </c>
+      <c r="N5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -810,15 +957,30 @@
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
-      <c r="F6" s="8">
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="8">
         <f>IF(D6="","",D6-C6)</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="J6" s="8">
         <f>IF(E6="","",E6-C6)</f>
         <v/>
       </c>
-      <c r="H6" s="6" t="n"/>
+      <c r="K6" s="8">
+        <f>IF(F6="","",F6-C6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="8">
+        <f>IF(G6="","",G6-C6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="8">
+        <f>IF(H6="","",H6-C6)</f>
+        <v/>
+      </c>
+      <c r="N6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -836,15 +998,30 @@
       </c>
       <c r="D7" s="7" t="n"/>
       <c r="E7" s="7" t="n"/>
-      <c r="F7" s="8">
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="7" t="n"/>
+      <c r="I7" s="8">
         <f>IF(D7="","",D7-C7)</f>
         <v/>
       </c>
-      <c r="G7" s="8">
+      <c r="J7" s="8">
         <f>IF(E7="","",E7-C7)</f>
         <v/>
       </c>
-      <c r="H7" s="6" t="n"/>
+      <c r="K7" s="8">
+        <f>IF(F7="","",F7-C7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="8">
+        <f>IF(G7="","",G7-C7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="8">
+        <f>IF(H7="","",H7-C7)</f>
+        <v/>
+      </c>
+      <c r="N7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -862,15 +1039,30 @@
       </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
-      <c r="F8" s="8">
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="8">
         <f>IF(D8="","",D8-C8)</f>
         <v/>
       </c>
-      <c r="G8" s="8">
+      <c r="J8" s="8">
         <f>IF(E8="","",E8-C8)</f>
         <v/>
       </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="K8" s="8">
+        <f>IF(F8="","",F8-C8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="8">
+        <f>IF(G8="","",G8-C8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="8">
+        <f>IF(H8="","",H8-C8)</f>
+        <v/>
+      </c>
+      <c r="N8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -888,15 +1080,30 @@
       </c>
       <c r="D9" s="7" t="n"/>
       <c r="E9" s="7" t="n"/>
-      <c r="F9" s="8">
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="8">
         <f>IF(D9="","",D9-C9)</f>
         <v/>
       </c>
-      <c r="G9" s="8">
+      <c r="J9" s="8">
         <f>IF(E9="","",E9-C9)</f>
         <v/>
       </c>
-      <c r="H9" s="6" t="n"/>
+      <c r="K9" s="8">
+        <f>IF(F9="","",F9-C9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="8">
+        <f>IF(G9="","",G9-C9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="8">
+        <f>IF(H9="","",H9-C9)</f>
+        <v/>
+      </c>
+      <c r="N9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -914,15 +1121,30 @@
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
-      <c r="F10" s="8">
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="8">
         <f>IF(D10="","",D10-C10)</f>
         <v/>
       </c>
-      <c r="G10" s="8">
+      <c r="J10" s="8">
         <f>IF(E10="","",E10-C10)</f>
         <v/>
       </c>
-      <c r="H10" s="6" t="n"/>
+      <c r="K10" s="8">
+        <f>IF(F10="","",F10-C10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="8">
+        <f>IF(G10="","",G10-C10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="8">
+        <f>IF(H10="","",H10-C10)</f>
+        <v/>
+      </c>
+      <c r="N10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -940,15 +1162,30 @@
       </c>
       <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
-      <c r="F11" s="8">
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="8">
         <f>IF(D11="","",D11-C11)</f>
         <v/>
       </c>
-      <c r="G11" s="8">
+      <c r="J11" s="8">
         <f>IF(E11="","",E11-C11)</f>
         <v/>
       </c>
-      <c r="H11" s="6" t="n"/>
+      <c r="K11" s="8">
+        <f>IF(F11="","",F11-C11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="8">
+        <f>IF(G11="","",G11-C11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="8">
+        <f>IF(H11="","",H11-C11)</f>
+        <v/>
+      </c>
+      <c r="N11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -966,15 +1203,30 @@
       </c>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
-      <c r="F12" s="8">
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="8">
         <f>IF(D12="","",D12-C12)</f>
         <v/>
       </c>
-      <c r="G12" s="8">
+      <c r="J12" s="8">
         <f>IF(E12="","",E12-C12)</f>
         <v/>
       </c>
-      <c r="H12" s="6" t="n"/>
+      <c r="K12" s="8">
+        <f>IF(F12="","",F12-C12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="8">
+        <f>IF(G12="","",G12-C12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="8">
+        <f>IF(H12="","",H12-C12)</f>
+        <v/>
+      </c>
+      <c r="N12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -992,15 +1244,30 @@
       </c>
       <c r="D13" s="7" t="n"/>
       <c r="E13" s="7" t="n"/>
-      <c r="F13" s="8">
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="8">
         <f>IF(D13="","",D13-C13)</f>
         <v/>
       </c>
-      <c r="G13" s="8">
+      <c r="J13" s="8">
         <f>IF(E13="","",E13-C13)</f>
         <v/>
       </c>
-      <c r="H13" s="6" t="n"/>
+      <c r="K13" s="8">
+        <f>IF(F13="","",F13-C13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="8">
+        <f>IF(G13="","",G13-C13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="8">
+        <f>IF(H13="","",H13-C13)</f>
+        <v/>
+      </c>
+      <c r="N13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1018,15 +1285,30 @@
       </c>
       <c r="D14" s="7" t="n"/>
       <c r="E14" s="7" t="n"/>
-      <c r="F14" s="8">
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="8">
         <f>IF(D14="","",D14-C14)</f>
         <v/>
       </c>
-      <c r="G14" s="8">
+      <c r="J14" s="8">
         <f>IF(E14="","",E14-C14)</f>
         <v/>
       </c>
-      <c r="H14" s="6" t="n"/>
+      <c r="K14" s="8">
+        <f>IF(F14="","",F14-C14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="8">
+        <f>IF(G14="","",G14-C14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="8">
+        <f>IF(H14="","",H14-C14)</f>
+        <v/>
+      </c>
+      <c r="N14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1044,15 +1326,30 @@
       </c>
       <c r="D15" s="7" t="n"/>
       <c r="E15" s="7" t="n"/>
-      <c r="F15" s="8">
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="8">
         <f>IF(D15="","",D15-C15)</f>
         <v/>
       </c>
-      <c r="G15" s="8">
+      <c r="J15" s="8">
         <f>IF(E15="","",E15-C15)</f>
         <v/>
       </c>
-      <c r="H15" s="6" t="n"/>
+      <c r="K15" s="8">
+        <f>IF(F15="","",F15-C15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="8">
+        <f>IF(G15="","",G15-C15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="8">
+        <f>IF(H15="","",H15-C15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1070,15 +1367,30 @@
       </c>
       <c r="D16" s="7" t="n"/>
       <c r="E16" s="7" t="n"/>
-      <c r="F16" s="8">
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="8">
         <f>IF(D16="","",D16-C16)</f>
         <v/>
       </c>
-      <c r="G16" s="8">
+      <c r="J16" s="8">
         <f>IF(E16="","",E16-C16)</f>
         <v/>
       </c>
-      <c r="H16" s="6" t="n"/>
+      <c r="K16" s="8">
+        <f>IF(F16="","",F16-C16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="8">
+        <f>IF(G16="","",G16-C16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="8">
+        <f>IF(H16="","",H16-C16)</f>
+        <v/>
+      </c>
+      <c r="N16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1096,15 +1408,30 @@
       </c>
       <c r="D17" s="7" t="n"/>
       <c r="E17" s="7" t="n"/>
-      <c r="F17" s="8">
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="8">
         <f>IF(D17="","",D17-C17)</f>
         <v/>
       </c>
-      <c r="G17" s="8">
+      <c r="J17" s="8">
         <f>IF(E17="","",E17-C17)</f>
         <v/>
       </c>
-      <c r="H17" s="6" t="n"/>
+      <c r="K17" s="8">
+        <f>IF(F17="","",F17-C17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="8">
+        <f>IF(G17="","",G17-C17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="8">
+        <f>IF(H17="","",H17-C17)</f>
+        <v/>
+      </c>
+      <c r="N17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1122,15 +1449,30 @@
       </c>
       <c r="D18" s="7" t="n"/>
       <c r="E18" s="7" t="n"/>
-      <c r="F18" s="8">
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="8">
         <f>IF(D18="","",D18-C18)</f>
         <v/>
       </c>
-      <c r="G18" s="8">
+      <c r="J18" s="8">
         <f>IF(E18="","",E18-C18)</f>
         <v/>
       </c>
-      <c r="H18" s="6" t="n"/>
+      <c r="K18" s="8">
+        <f>IF(F18="","",F18-C18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="8">
+        <f>IF(G18="","",G18-C18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="8">
+        <f>IF(H18="","",H18-C18)</f>
+        <v/>
+      </c>
+      <c r="N18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1148,15 +1490,30 @@
       </c>
       <c r="D19" s="7" t="n"/>
       <c r="E19" s="7" t="n"/>
-      <c r="F19" s="8">
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="8">
         <f>IF(D19="","",D19-C19)</f>
         <v/>
       </c>
-      <c r="G19" s="8">
+      <c r="J19" s="8">
         <f>IF(E19="","",E19-C19)</f>
         <v/>
       </c>
-      <c r="H19" s="6" t="n"/>
+      <c r="K19" s="8">
+        <f>IF(F19="","",F19-C19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="8">
+        <f>IF(G19="","",G19-C19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="8">
+        <f>IF(H19="","",H19-C19)</f>
+        <v/>
+      </c>
+      <c r="N19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1174,15 +1531,30 @@
       </c>
       <c r="D20" s="7" t="n"/>
       <c r="E20" s="7" t="n"/>
-      <c r="F20" s="8">
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="8">
         <f>IF(D20="","",D20-C20)</f>
         <v/>
       </c>
-      <c r="G20" s="8">
+      <c r="J20" s="8">
         <f>IF(E20="","",E20-C20)</f>
         <v/>
       </c>
-      <c r="H20" s="6" t="n"/>
+      <c r="K20" s="8">
+        <f>IF(F20="","",F20-C20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="8">
+        <f>IF(G20="","",G20-C20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="8">
+        <f>IF(H20="","",H20-C20)</f>
+        <v/>
+      </c>
+      <c r="N20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1200,15 +1572,30 @@
       </c>
       <c r="D21" s="7" t="n"/>
       <c r="E21" s="7" t="n"/>
-      <c r="F21" s="8">
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="8">
         <f>IF(D21="","",D21-C21)</f>
         <v/>
       </c>
-      <c r="G21" s="8">
+      <c r="J21" s="8">
         <f>IF(E21="","",E21-C21)</f>
         <v/>
       </c>
-      <c r="H21" s="6" t="n"/>
+      <c r="K21" s="8">
+        <f>IF(F21="","",F21-C21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="8">
+        <f>IF(G21="","",G21-C21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="8">
+        <f>IF(H21="","",H21-C21)</f>
+        <v/>
+      </c>
+      <c r="N21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1226,15 +1613,30 @@
       </c>
       <c r="D22" s="7" t="n"/>
       <c r="E22" s="7" t="n"/>
-      <c r="F22" s="8">
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="8">
         <f>IF(D22="","",D22-C22)</f>
         <v/>
       </c>
-      <c r="G22" s="8">
+      <c r="J22" s="8">
         <f>IF(E22="","",E22-C22)</f>
         <v/>
       </c>
-      <c r="H22" s="6" t="n"/>
+      <c r="K22" s="8">
+        <f>IF(F22="","",F22-C22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="8">
+        <f>IF(G22="","",G22-C22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="8">
+        <f>IF(H22="","",H22-C22)</f>
+        <v/>
+      </c>
+      <c r="N22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1252,15 +1654,30 @@
       </c>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
-      <c r="F23" s="8">
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="8">
         <f>IF(D23="","",D23-C23)</f>
         <v/>
       </c>
-      <c r="G23" s="8">
+      <c r="J23" s="8">
         <f>IF(E23="","",E23-C23)</f>
         <v/>
       </c>
-      <c r="H23" s="6" t="n"/>
+      <c r="K23" s="8">
+        <f>IF(F23="","",F23-C23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="8">
+        <f>IF(G23="","",G23-C23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="8">
+        <f>IF(H23="","",H23-C23)</f>
+        <v/>
+      </c>
+      <c r="N23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1278,15 +1695,30 @@
       </c>
       <c r="D24" s="7" t="n"/>
       <c r="E24" s="7" t="n"/>
-      <c r="F24" s="8">
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="8">
         <f>IF(D24="","",D24-C24)</f>
         <v/>
       </c>
-      <c r="G24" s="8">
+      <c r="J24" s="8">
         <f>IF(E24="","",E24-C24)</f>
         <v/>
       </c>
-      <c r="H24" s="6" t="n"/>
+      <c r="K24" s="8">
+        <f>IF(F24="","",F24-C24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="8">
+        <f>IF(G24="","",G24-C24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="8">
+        <f>IF(H24="","",H24-C24)</f>
+        <v/>
+      </c>
+      <c r="N24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1304,15 +1736,30 @@
       </c>
       <c r="D25" s="7" t="n"/>
       <c r="E25" s="7" t="n"/>
-      <c r="F25" s="8">
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="8">
         <f>IF(D25="","",D25-C25)</f>
         <v/>
       </c>
-      <c r="G25" s="8">
+      <c r="J25" s="8">
         <f>IF(E25="","",E25-C25)</f>
         <v/>
       </c>
-      <c r="H25" s="6" t="n"/>
+      <c r="K25" s="8">
+        <f>IF(F25="","",F25-C25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="8">
+        <f>IF(G25="","",G25-C25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="8">
+        <f>IF(H25="","",H25-C25)</f>
+        <v/>
+      </c>
+      <c r="N25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1330,15 +1777,30 @@
       </c>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
-      <c r="F26" s="8">
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="8">
         <f>IF(D26="","",D26-C26)</f>
         <v/>
       </c>
-      <c r="G26" s="8">
+      <c r="J26" s="8">
         <f>IF(E26="","",E26-C26)</f>
         <v/>
       </c>
-      <c r="H26" s="6" t="n"/>
+      <c r="K26" s="8">
+        <f>IF(F26="","",F26-C26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="8">
+        <f>IF(G26="","",G26-C26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="8">
+        <f>IF(H26="","",H26-C26)</f>
+        <v/>
+      </c>
+      <c r="N26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1356,15 +1818,30 @@
       </c>
       <c r="D27" s="7" t="n"/>
       <c r="E27" s="7" t="n"/>
-      <c r="F27" s="8">
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="8">
         <f>IF(D27="","",D27-C27)</f>
         <v/>
       </c>
-      <c r="G27" s="8">
+      <c r="J27" s="8">
         <f>IF(E27="","",E27-C27)</f>
         <v/>
       </c>
-      <c r="H27" s="6" t="n"/>
+      <c r="K27" s="8">
+        <f>IF(F27="","",F27-C27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="8">
+        <f>IF(G27="","",G27-C27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="8">
+        <f>IF(H27="","",H27-C27)</f>
+        <v/>
+      </c>
+      <c r="N27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1382,15 +1859,30 @@
       </c>
       <c r="D28" s="7" t="n"/>
       <c r="E28" s="7" t="n"/>
-      <c r="F28" s="8">
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="8">
         <f>IF(D28="","",D28-C28)</f>
         <v/>
       </c>
-      <c r="G28" s="8">
+      <c r="J28" s="8">
         <f>IF(E28="","",E28-C28)</f>
         <v/>
       </c>
-      <c r="H28" s="6" t="n"/>
+      <c r="K28" s="8">
+        <f>IF(F28="","",F28-C28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="8">
+        <f>IF(G28="","",G28-C28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="8">
+        <f>IF(H28="","",H28-C28)</f>
+        <v/>
+      </c>
+      <c r="N28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1408,15 +1900,30 @@
       </c>
       <c r="D29" s="7" t="n"/>
       <c r="E29" s="7" t="n"/>
-      <c r="F29" s="8">
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="n"/>
+      <c r="I29" s="8">
         <f>IF(D29="","",D29-C29)</f>
         <v/>
       </c>
-      <c r="G29" s="8">
+      <c r="J29" s="8">
         <f>IF(E29="","",E29-C29)</f>
         <v/>
       </c>
-      <c r="H29" s="6" t="n"/>
+      <c r="K29" s="8">
+        <f>IF(F29="","",F29-C29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="8">
+        <f>IF(G29="","",G29-C29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="8">
+        <f>IF(H29="","",H29-C29)</f>
+        <v/>
+      </c>
+      <c r="N29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1434,15 +1941,30 @@
       </c>
       <c r="D30" s="7" t="n"/>
       <c r="E30" s="7" t="n"/>
-      <c r="F30" s="8">
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="8">
         <f>IF(D30="","",D30-C30)</f>
         <v/>
       </c>
-      <c r="G30" s="8">
+      <c r="J30" s="8">
         <f>IF(E30="","",E30-C30)</f>
         <v/>
       </c>
-      <c r="H30" s="6" t="n"/>
+      <c r="K30" s="8">
+        <f>IF(F30="","",F30-C30)</f>
+        <v/>
+      </c>
+      <c r="L30" s="8">
+        <f>IF(G30="","",G30-C30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="8">
+        <f>IF(H30="","",H30-C30)</f>
+        <v/>
+      </c>
+      <c r="N30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1460,15 +1982,30 @@
       </c>
       <c r="D31" s="7" t="n"/>
       <c r="E31" s="7" t="n"/>
-      <c r="F31" s="8">
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="7" t="n"/>
+      <c r="I31" s="8">
         <f>IF(D31="","",D31-C31)</f>
         <v/>
       </c>
-      <c r="G31" s="8">
+      <c r="J31" s="8">
         <f>IF(E31="","",E31-C31)</f>
         <v/>
       </c>
-      <c r="H31" s="6" t="n"/>
+      <c r="K31" s="8">
+        <f>IF(F31="","",F31-C31)</f>
+        <v/>
+      </c>
+      <c r="L31" s="8">
+        <f>IF(G31="","",G31-C31)</f>
+        <v/>
+      </c>
+      <c r="M31" s="8">
+        <f>IF(H31="","",H31-C31)</f>
+        <v/>
+      </c>
+      <c r="N31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1486,15 +2023,30 @@
       </c>
       <c r="D32" s="7" t="n"/>
       <c r="E32" s="7" t="n"/>
-      <c r="F32" s="8">
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="8">
         <f>IF(D32="","",D32-C32)</f>
         <v/>
       </c>
-      <c r="G32" s="8">
+      <c r="J32" s="8">
         <f>IF(E32="","",E32-C32)</f>
         <v/>
       </c>
-      <c r="H32" s="6" t="n"/>
+      <c r="K32" s="8">
+        <f>IF(F32="","",F32-C32)</f>
+        <v/>
+      </c>
+      <c r="L32" s="8">
+        <f>IF(G32="","",G32-C32)</f>
+        <v/>
+      </c>
+      <c r="M32" s="8">
+        <f>IF(H32="","",H32-C32)</f>
+        <v/>
+      </c>
+      <c r="N32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1512,15 +2064,30 @@
       </c>
       <c r="D33" s="7" t="n"/>
       <c r="E33" s="7" t="n"/>
-      <c r="F33" s="8">
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="8">
         <f>IF(D33="","",D33-C33)</f>
         <v/>
       </c>
-      <c r="G33" s="8">
+      <c r="J33" s="8">
         <f>IF(E33="","",E33-C33)</f>
         <v/>
       </c>
-      <c r="H33" s="6" t="n"/>
+      <c r="K33" s="8">
+        <f>IF(F33="","",F33-C33)</f>
+        <v/>
+      </c>
+      <c r="L33" s="8">
+        <f>IF(G33="","",G33-C33)</f>
+        <v/>
+      </c>
+      <c r="M33" s="8">
+        <f>IF(H33="","",H33-C33)</f>
+        <v/>
+      </c>
+      <c r="N33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1538,15 +2105,30 @@
       </c>
       <c r="D34" s="7" t="n"/>
       <c r="E34" s="7" t="n"/>
-      <c r="F34" s="8">
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="7" t="n"/>
+      <c r="I34" s="8">
         <f>IF(D34="","",D34-C34)</f>
         <v/>
       </c>
-      <c r="G34" s="8">
+      <c r="J34" s="8">
         <f>IF(E34="","",E34-C34)</f>
         <v/>
       </c>
-      <c r="H34" s="6" t="n"/>
+      <c r="K34" s="8">
+        <f>IF(F34="","",F34-C34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="8">
+        <f>IF(G34="","",G34-C34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="8">
+        <f>IF(H34="","",H34-C34)</f>
+        <v/>
+      </c>
+      <c r="N34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1564,15 +2146,30 @@
       </c>
       <c r="D35" s="7" t="n"/>
       <c r="E35" s="7" t="n"/>
-      <c r="F35" s="8">
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="8">
         <f>IF(D35="","",D35-C35)</f>
         <v/>
       </c>
-      <c r="G35" s="8">
+      <c r="J35" s="8">
         <f>IF(E35="","",E35-C35)</f>
         <v/>
       </c>
-      <c r="H35" s="6" t="n"/>
+      <c r="K35" s="8">
+        <f>IF(F35="","",F35-C35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="8">
+        <f>IF(G35="","",G35-C35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="8">
+        <f>IF(H35="","",H35-C35)</f>
+        <v/>
+      </c>
+      <c r="N35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1590,15 +2187,30 @@
       </c>
       <c r="D36" s="7" t="n"/>
       <c r="E36" s="7" t="n"/>
-      <c r="F36" s="8">
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="8">
         <f>IF(D36="","",D36-C36)</f>
         <v/>
       </c>
-      <c r="G36" s="8">
+      <c r="J36" s="8">
         <f>IF(E36="","",E36-C36)</f>
         <v/>
       </c>
-      <c r="H36" s="6" t="n"/>
+      <c r="K36" s="8">
+        <f>IF(F36="","",F36-C36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="8">
+        <f>IF(G36="","",G36-C36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="8">
+        <f>IF(H36="","",H36-C36)</f>
+        <v/>
+      </c>
+      <c r="N36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1616,15 +2228,30 @@
       </c>
       <c r="D37" s="7" t="n"/>
       <c r="E37" s="7" t="n"/>
-      <c r="F37" s="8">
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="8">
         <f>IF(D37="","",D37-C37)</f>
         <v/>
       </c>
-      <c r="G37" s="8">
+      <c r="J37" s="8">
         <f>IF(E37="","",E37-C37)</f>
         <v/>
       </c>
-      <c r="H37" s="6" t="n"/>
+      <c r="K37" s="8">
+        <f>IF(F37="","",F37-C37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="8">
+        <f>IF(G37="","",G37-C37)</f>
+        <v/>
+      </c>
+      <c r="M37" s="8">
+        <f>IF(H37="","",H37-C37)</f>
+        <v/>
+      </c>
+      <c r="N37" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1658,13 +2285,49 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:G37">
-    <cfRule type="cellIs" priority="3" operator="lessThan" dxfId="0">
+  <conditionalFormatting sqref="F5:F37">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="00F8CBAD"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00A9D08E"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G37">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="00F8CBAD"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00A9D08E"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H37">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="num" val="1"/>
+        <cfvo type="num" val="3"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="00F8CBAD"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00A9D08E"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5:M37">
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C5:E37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="1〜5の整数を入力してください" type="whole" operator="between">
+    <dataValidation sqref="C5:H37" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="入力エラー" error="1〜5の整数を入力してください" type="whole" operator="between">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -1679,13 +2342,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1716,6 +2382,21 @@
           <t>HS</t>
         </is>
       </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1735,6 +2416,18 @@
         <f>IFERROR(AVERAGEIFS(スキルマップ!$E$5:$E$37,スキルマップ!$A$5:$A$37,$A4),0)</f>
         <v/>
       </c>
+      <c r="E4" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$F$5:$F$37,スキルマップ!$A$5:$A$37,$A4),0)</f>
+        <v/>
+      </c>
+      <c r="F4" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A4),0)</f>
+        <v/>
+      </c>
+      <c r="G4" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A4),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1754,6 +2447,18 @@
         <f>IFERROR(AVERAGEIFS(スキルマップ!$E$5:$E$37,スキルマップ!$A$5:$A$37,$A5),0)</f>
         <v/>
       </c>
+      <c r="E5" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$F$5:$F$37,スキルマップ!$A$5:$A$37,$A5),0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A5),0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A5),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1773,6 +2478,18 @@
         <f>IFERROR(AVERAGEIFS(スキルマップ!$E$5:$E$37,スキルマップ!$A$5:$A$37,$A6),0)</f>
         <v/>
       </c>
+      <c r="E6" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$F$5:$F$37,スキルマップ!$A$5:$A$37,$A6),0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A6),0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A6),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1792,6 +2509,18 @@
         <f>IFERROR(AVERAGEIFS(スキルマップ!$E$5:$E$37,スキルマップ!$A$5:$A$37,$A7),0)</f>
         <v/>
       </c>
+      <c r="E7" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$F$5:$F$37,スキルマップ!$A$5:$A$37,$A7),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A7),0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A7),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1811,6 +2540,18 @@
         <f>IFERROR(AVERAGEIFS(スキルマップ!$E$5:$E$37,スキルマップ!$A$5:$A$37,$A8),0)</f>
         <v/>
       </c>
+      <c r="E8" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$F$5:$F$37,スキルマップ!$A$5:$A$37,$A8),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A8),0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A8),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1830,6 +2571,18 @@
         <f>IFERROR(AVERAGEIFS(スキルマップ!$E$5:$E$37,スキルマップ!$A$5:$A$37,$A9),0)</f>
         <v/>
       </c>
+      <c r="E9" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$F$5:$F$37,スキルマップ!$A$5:$A$37,$A9),0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A9),0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
+        <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A9),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1847,6 +2600,18 @@
       </c>
       <c r="D10" s="11">
         <f>IFERROR(AVERAGE(スキルマップ!$E$5:$E$37),0)</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>IFERROR(AVERAGE(スキルマップ!$F$5:$F$37),0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>IFERROR(AVERAGE(スキルマップ!$G$5:$G$37),0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IFERROR(AVERAGE(スキルマップ!$H$5:$H$37),0)</f>
         <v/>
       </c>
     </row>

--- a/skillmap/スキルマップ.xlsx
+++ b/skillmap/スキルマップ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codeWork\skillmap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245C3293-83C3-4CA0-85D4-CCFAFA176F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEB4D99-B7AD-400A-99F1-0C56E017F54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -766,7 +766,7 @@
                   <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5</c:v>
+                  <c:v>4.4000000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -832,22 +832,22 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>3.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -913,22 +913,22 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>4.2857142857142856</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.1666666666666665</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>2.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3.8333333333333335</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>2.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1410,8 +1410,12 @@
       <c r="F5" s="7">
         <v>5</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="G5" s="7">
+        <v>5</v>
+      </c>
+      <c r="H5" s="7">
+        <v>4</v>
+      </c>
       <c r="I5" s="8">
         <f t="shared" ref="I5:I37" si="0">IF(D5="","",D5-C5)</f>
         <v>-1</v>
@@ -1424,13 +1428,13 @@
         <f t="shared" ref="K5:K37" si="2">IF(F5="","",F5-C5)</f>
         <v>2</v>
       </c>
-      <c r="L5" s="8" t="str">
+      <c r="L5" s="8">
         <f t="shared" ref="L5:L37" si="3">IF(G5="","",G5-C5)</f>
-        <v/>
-      </c>
-      <c r="M5" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M5" s="8">
         <f t="shared" ref="M5:M37" si="4">IF(H5="","",H5-C5)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N5" s="6"/>
     </row>
@@ -1453,8 +1457,12 @@
       <c r="F6" s="7">
         <v>5</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+      <c r="G6" s="7">
+        <v>5</v>
+      </c>
+      <c r="H6" s="7">
+        <v>5</v>
+      </c>
       <c r="I6" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1467,13 +1475,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L6" s="8" t="str">
+      <c r="L6" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M6" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M6" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="N6" s="6"/>
     </row>
@@ -1496,8 +1504,12 @@
       <c r="F7" s="7">
         <v>5</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="G7" s="7">
+        <v>5</v>
+      </c>
+      <c r="H7" s="7">
+        <v>5</v>
+      </c>
       <c r="I7" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1510,13 +1522,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L7" s="8" t="str">
+      <c r="L7" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M7" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M7" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="N7" s="6"/>
     </row>
@@ -1539,8 +1551,12 @@
       <c r="F8" s="7">
         <v>5</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="G8" s="7">
+        <v>5</v>
+      </c>
+      <c r="H8" s="7">
+        <v>4</v>
+      </c>
       <c r="I8" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1553,13 +1569,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L8" s="8" t="str">
+      <c r="L8" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M8" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M8" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N8" s="6"/>
     </row>
@@ -1582,8 +1598,12 @@
       <c r="F9" s="7">
         <v>5</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="G9" s="7">
+        <v>5</v>
+      </c>
+      <c r="H9" s="7">
+        <v>5</v>
+      </c>
       <c r="I9" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1596,13 +1616,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L9" s="8" t="str">
+      <c r="L9" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M9" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M9" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="N9" s="6"/>
     </row>
@@ -1625,8 +1645,12 @@
       <c r="F10" s="7">
         <v>5</v>
       </c>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="G10" s="7">
+        <v>5</v>
+      </c>
+      <c r="H10" s="7">
+        <v>5</v>
+      </c>
       <c r="I10" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1639,13 +1663,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L10" s="8" t="str">
+      <c r="L10" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M10" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M10" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="N10" s="6"/>
     </row>
@@ -1668,8 +1692,12 @@
       <c r="F11" s="7">
         <v>3</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="G11" s="7">
+        <v>5</v>
+      </c>
+      <c r="H11" s="7">
+        <v>2</v>
+      </c>
       <c r="I11" s="8">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -1682,13 +1710,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L11" s="8" t="str">
+      <c r="L11" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M11" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M11" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="N11" s="6"/>
     </row>
@@ -1711,8 +1739,12 @@
       <c r="F12" s="7">
         <v>5</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="G12" s="7">
+        <v>5</v>
+      </c>
+      <c r="H12" s="7">
+        <v>4</v>
+      </c>
       <c r="I12" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1725,13 +1757,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L12" s="8" t="str">
+      <c r="L12" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M12" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M12" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N12" s="6"/>
     </row>
@@ -1754,8 +1786,12 @@
       <c r="F13" s="7">
         <v>5</v>
       </c>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="G13" s="7">
+        <v>5</v>
+      </c>
+      <c r="H13" s="7">
+        <v>4</v>
+      </c>
       <c r="I13" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1768,13 +1804,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L13" s="8" t="str">
+      <c r="L13" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M13" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M13" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N13" s="6"/>
     </row>
@@ -1797,8 +1833,12 @@
       <c r="F14" s="7">
         <v>5</v>
       </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="G14" s="7">
+        <v>5</v>
+      </c>
+      <c r="H14" s="7">
+        <v>4</v>
+      </c>
       <c r="I14" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1811,13 +1851,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L14" s="8" t="str">
+      <c r="L14" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M14" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M14" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N14" s="6"/>
     </row>
@@ -1840,8 +1880,12 @@
       <c r="F15" s="7">
         <v>4</v>
       </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="G15" s="7">
+        <v>5</v>
+      </c>
+      <c r="H15" s="7">
+        <v>4</v>
+      </c>
       <c r="I15" s="8">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -1854,13 +1898,13 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L15" s="8" t="str">
+      <c r="L15" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M15" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M15" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N15" s="6"/>
     </row>
@@ -1883,8 +1927,12 @@
       <c r="F16" s="7">
         <v>5</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="G16" s="7">
+        <v>5</v>
+      </c>
+      <c r="H16" s="7">
+        <v>4</v>
+      </c>
       <c r="I16" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1897,13 +1945,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L16" s="8" t="str">
+      <c r="L16" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M16" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M16" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N16" s="6"/>
     </row>
@@ -1926,8 +1974,12 @@
       <c r="F17" s="7">
         <v>5</v>
       </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="G17" s="7">
+        <v>5</v>
+      </c>
+      <c r="H17" s="7">
+        <v>4</v>
+      </c>
       <c r="I17" s="8">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -1940,13 +1992,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L17" s="8" t="str">
+      <c r="L17" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M17" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M17" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N17" s="6"/>
     </row>
@@ -1970,7 +2022,9 @@
         <v>2</v>
       </c>
       <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+      <c r="H18" s="7">
+        <v>1</v>
+      </c>
       <c r="I18" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -1983,13 +2037,12 @@
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="L18" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M18" s="8" t="str">
+      <c r="L18" s="8">
+        <v>3</v>
+      </c>
+      <c r="M18" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>-2</v>
       </c>
       <c r="N18" s="6"/>
     </row>
@@ -2012,8 +2065,12 @@
       <c r="F19" s="7">
         <v>5</v>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="G19" s="7">
+        <v>5</v>
+      </c>
+      <c r="H19" s="7">
+        <v>4</v>
+      </c>
       <c r="I19" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2026,13 +2083,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L19" s="8" t="str">
+      <c r="L19" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M19" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M19" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N19" s="6"/>
     </row>
@@ -2055,8 +2112,12 @@
       <c r="F20" s="7">
         <v>4</v>
       </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="G20" s="7">
+        <v>5</v>
+      </c>
+      <c r="H20" s="7">
+        <v>2</v>
+      </c>
       <c r="I20" s="8">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -2069,13 +2130,13 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L20" s="8" t="str">
+      <c r="L20" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M20" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M20" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="N20" s="6"/>
     </row>
@@ -2098,8 +2159,12 @@
       <c r="F21" s="7">
         <v>4</v>
       </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="G21" s="7">
+        <v>5</v>
+      </c>
+      <c r="H21" s="7">
+        <v>4</v>
+      </c>
       <c r="I21" s="8">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -2112,13 +2177,13 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L21" s="8" t="str">
+      <c r="L21" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M21" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M21" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N21" s="6"/>
     </row>
@@ -2141,8 +2206,12 @@
       <c r="F22" s="7">
         <v>5</v>
       </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+      <c r="G22" s="7">
+        <v>5</v>
+      </c>
+      <c r="H22" s="7">
+        <v>4</v>
+      </c>
       <c r="I22" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2155,13 +2224,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L22" s="8" t="str">
+      <c r="L22" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M22" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M22" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N22" s="6"/>
     </row>
@@ -2184,8 +2253,12 @@
       <c r="F23" s="7">
         <v>5</v>
       </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
+      <c r="G23" s="7">
+        <v>5</v>
+      </c>
+      <c r="H23" s="7">
+        <v>3</v>
+      </c>
       <c r="I23" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2198,13 +2271,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L23" s="8" t="str">
+      <c r="L23" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M23" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M23" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N23" s="6"/>
     </row>
@@ -2227,8 +2300,12 @@
       <c r="F24" s="7">
         <v>5</v>
       </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="G24" s="7">
+        <v>5</v>
+      </c>
+      <c r="H24" s="7">
+        <v>2</v>
+      </c>
       <c r="I24" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2241,13 +2318,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L24" s="8" t="str">
+      <c r="L24" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M24" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M24" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="N24" s="6"/>
     </row>
@@ -2270,8 +2347,12 @@
       <c r="F25" s="7">
         <v>3</v>
       </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="G25" s="7">
+        <v>5</v>
+      </c>
+      <c r="H25" s="7">
+        <v>2</v>
+      </c>
       <c r="I25" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2284,13 +2365,13 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="L25" s="8" t="str">
+      <c r="L25" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M25" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M25" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="N25" s="6"/>
     </row>
@@ -2313,8 +2394,12 @@
       <c r="F26" s="7">
         <v>5</v>
       </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="G26" s="7">
+        <v>5</v>
+      </c>
+      <c r="H26" s="7">
+        <v>3</v>
+      </c>
       <c r="I26" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2327,13 +2412,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L26" s="8" t="str">
+      <c r="L26" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M26" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M26" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N26" s="6"/>
     </row>
@@ -2356,8 +2441,12 @@
       <c r="F27" s="7">
         <v>5</v>
       </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="G27" s="7">
+        <v>5</v>
+      </c>
+      <c r="H27" s="7">
+        <v>3</v>
+      </c>
       <c r="I27" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2370,13 +2459,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L27" s="8" t="str">
+      <c r="L27" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M27" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M27" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N27" s="6"/>
     </row>
@@ -2399,8 +2488,12 @@
       <c r="F28" s="7">
         <v>5</v>
       </c>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="G28" s="7">
+        <v>5</v>
+      </c>
+      <c r="H28" s="7">
+        <v>4</v>
+      </c>
       <c r="I28" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2413,13 +2506,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L28" s="8" t="str">
+      <c r="L28" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M28" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M28" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N28" s="6"/>
     </row>
@@ -2442,8 +2535,12 @@
       <c r="F29" s="7">
         <v>5</v>
       </c>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
+      <c r="G29" s="7">
+        <v>5</v>
+      </c>
+      <c r="H29" s="7">
+        <v>4</v>
+      </c>
       <c r="I29" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2456,13 +2553,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L29" s="8" t="str">
+      <c r="L29" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M29" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M29" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N29" s="6"/>
     </row>
@@ -2485,8 +2582,12 @@
       <c r="F30" s="7">
         <v>5</v>
       </c>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="G30" s="7">
+        <v>5</v>
+      </c>
+      <c r="H30" s="7">
+        <v>4</v>
+      </c>
       <c r="I30" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2499,13 +2600,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L30" s="8" t="str">
+      <c r="L30" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M30" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M30" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N30" s="6"/>
     </row>
@@ -2528,8 +2629,12 @@
       <c r="F31" s="7">
         <v>5</v>
       </c>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="G31" s="7">
+        <v>5</v>
+      </c>
+      <c r="H31" s="7">
+        <v>4</v>
+      </c>
       <c r="I31" s="8">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -2542,13 +2647,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L31" s="8" t="str">
+      <c r="L31" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M31" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M31" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N31" s="6"/>
     </row>
@@ -2571,8 +2676,12 @@
       <c r="F32" s="7">
         <v>5</v>
       </c>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="G32" s="7">
+        <v>5</v>
+      </c>
+      <c r="H32" s="7">
+        <v>4</v>
+      </c>
       <c r="I32" s="8">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -2585,13 +2694,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L32" s="8" t="str">
+      <c r="L32" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M32" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M32" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N32" s="6"/>
     </row>
@@ -2614,8 +2723,12 @@
       <c r="F33" s="7">
         <v>5</v>
       </c>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
+      <c r="G33" s="7">
+        <v>3</v>
+      </c>
+      <c r="H33" s="7">
+        <v>3</v>
+      </c>
       <c r="I33" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2628,13 +2741,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L33" s="8" t="str">
+      <c r="L33" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M33" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="M33" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N33" s="6"/>
     </row>
@@ -2657,8 +2770,12 @@
       <c r="F34" s="7">
         <v>5</v>
       </c>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
+      <c r="G34" s="7">
+        <v>5</v>
+      </c>
+      <c r="H34" s="7">
+        <v>3</v>
+      </c>
       <c r="I34" s="8">
         <f t="shared" si="0"/>
         <v>-1</v>
@@ -2671,13 +2788,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L34" s="8" t="str">
+      <c r="L34" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M34" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="M34" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N34" s="6"/>
     </row>
@@ -2700,8 +2817,12 @@
       <c r="F35" s="7">
         <v>5</v>
       </c>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
+      <c r="G35" s="7">
+        <v>4</v>
+      </c>
+      <c r="H35" s="7">
+        <v>3</v>
+      </c>
       <c r="I35" s="8">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -2714,13 +2835,13 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L35" s="8" t="str">
+      <c r="L35" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M35" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="M35" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0</v>
       </c>
       <c r="N35" s="6"/>
     </row>
@@ -2741,10 +2862,14 @@
         <v>1</v>
       </c>
       <c r="F36" s="7">
-        <v>5</v>
-      </c>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="G36" s="7">
+        <v>3</v>
+      </c>
+      <c r="H36" s="7">
+        <v>2</v>
+      </c>
       <c r="I36" s="8">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -2755,15 +2880,15 @@
       </c>
       <c r="K36" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L36" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="L36" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M36" s="8" t="str">
+        <v>0</v>
+      </c>
+      <c r="M36" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="N36" s="6"/>
     </row>
@@ -2784,10 +2909,14 @@
         <v>2</v>
       </c>
       <c r="F37" s="7">
-        <v>5</v>
-      </c>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
+        <v>4</v>
+      </c>
+      <c r="G37" s="7">
+        <v>4</v>
+      </c>
+      <c r="H37" s="7">
+        <v>2</v>
+      </c>
       <c r="I37" s="8">
         <f t="shared" si="0"/>
         <v>-2</v>
@@ -2798,15 +2927,15 @@
       </c>
       <c r="K37" s="8">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L37" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="L37" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M37" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="M37" s="8">
         <f t="shared" si="4"/>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="N37" s="6"/>
     </row>
@@ -2951,11 +3080,11 @@
       </c>
       <c r="F4" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A4),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G4" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A4),0)</f>
-        <v>0</v>
+        <v>4.2857142857142856</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
@@ -2980,11 +3109,11 @@
       </c>
       <c r="F5" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A5),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A5),0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
@@ -3009,11 +3138,11 @@
       </c>
       <c r="F6" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A6),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A6),0)</f>
-        <v>0</v>
+        <v>3.1666666666666665</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
@@ -3038,11 +3167,11 @@
       </c>
       <c r="F7" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A7),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A7),0)</f>
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
@@ -3067,11 +3196,11 @@
       </c>
       <c r="F8" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A8),0)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A8),0)</f>
-        <v>0</v>
+        <v>3.8333333333333335</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
@@ -3092,15 +3221,15 @@
       </c>
       <c r="E9" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$F$5:$F$37,スキルマップ!$A$5:$A$37,$A9),0)</f>
-        <v>5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="F9" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$G$5:$G$37,スキルマップ!$A$5:$A$37,$A9),0)</f>
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="G9" s="9">
         <f>IFERROR(AVERAGEIFS(スキルマップ!$H$5:$H$37,スキルマップ!$A$5:$A$37,$A9),0)</f>
-        <v>0</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.25" x14ac:dyDescent="0.15">
@@ -3121,15 +3250,15 @@
       </c>
       <c r="E10" s="11">
         <f>IFERROR(AVERAGE(スキルマップ!$F$5:$F$37),0)</f>
-        <v>4.6969696969696972</v>
+        <v>4.6060606060606064</v>
       </c>
       <c r="F10" s="11">
         <f>IFERROR(AVERAGE(スキルマップ!$G$5:$G$37),0)</f>
-        <v>0</v>
+        <v>4.8125</v>
       </c>
       <c r="G10" s="11">
         <f>IFERROR(AVERAGE(スキルマップ!$H$5:$H$37),0)</f>
-        <v>0</v>
+        <v>3.4848484848484849</v>
       </c>
     </row>
   </sheetData>
